--- a/outputs/334-11.xlsx
+++ b/outputs/334-11.xlsx
@@ -104,12 +104,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -305,31 +309,31 @@
   <dimension ref="C1:C5"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>-12671.88</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>-19666.7</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="1" t="n">
         <v>-14269.55</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C5" s="1"/>
+      <c r="C5" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/outputs/334-11.xlsx
+++ b/outputs/334-11.xlsx
@@ -318,22 +318,24 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C2" s="2" t="n">
+      <c r="C2" s="1" t="n">
         <v>-12671.88</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3" s="2" t="n">
-        <v>-19666.7</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4" s="1" t="n">
+        <v>-19666.7</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C5" s="1" t="n">
         <v>-14269.55</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C5" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
